--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484567_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484567_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.54</v>
+        <v>3.3043</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2509</v>
+        <v>3.8418</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.711</v>
+        <v>-0.5376</v>
       </c>
       <c r="G2" t="n">
         <v>2.4615</v>
@@ -610,13 +610,13 @@
         <v>2.7489</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7177</v>
+        <v>-0.9534</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4132</v>
+        <v>-0.8224</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3045</v>
+        <v>-0.1311</v>
       </c>
       <c r="V2" t="n">
         <v>1.9794</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9053</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3528</v>
+        <v>1.1605</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3543</v>
+        <v>-0.2552</v>
       </c>
       <c r="G3" t="n">
         <v>0.3916</v>
@@ -688,13 +688,13 @@
         <v>0.5498</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3775</v>
+        <v>0.2843</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4208</v>
+        <v>0.2285</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0433</v>
+        <v>0.0558</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1371</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4756</v>
+        <v>0.2115</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3299</v>
+        <v>1.2888</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-1.0773</v>
       </c>
       <c r="G4" t="n">
         <v>0.5805</v>
@@ -766,13 +766,13 @@
         <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0897</v>
+        <v>-0.1744</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1847</v>
+        <v>-0.2259</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2744</v>
+        <v>0.0515</v>
       </c>
       <c r="V4" t="n">
         <v>-2.0272</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. HOLGADO CUELLAR</t>
+          <t>D. ARIJA DE LA PENA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8633</v>
+        <v>-0.3332</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.169</v>
+        <v>0.0927</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6943</v>
+        <v>-0.4258</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.9932</v>
+        <v>-1.792</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8328</v>
+        <v>0.2306</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.1604</v>
+        <v>-2.0226</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.7964</v>
+        <v>1.1496</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0433</v>
+        <v>2.9477</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.8397</v>
+        <v>-1.7981</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1968</v>
+        <v>-2.9416</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8762</v>
+        <v>-2.7171</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3207</v>
+        <v>-0.2246</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1833</v>
+        <v>0.5498</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>-2.0158</v>
       </c>
       <c r="R5" t="n">
-        <v>0.733</v>
+        <v>2.5656</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5427</v>
+        <v>-0.4265</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3122</v>
+        <v>-0.6301</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2305</v>
+        <v>0.2036</v>
       </c>
       <c r="V5" t="n">
-        <v>2.8559</v>
+        <v>1.3355</v>
       </c>
       <c r="W5" t="n">
-        <v>2.8559</v>
+        <v>1.5889</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2534</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. IGUAL BAU</t>
+          <t>R. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9139</v>
+        <v>-0.3711</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0632</v>
+        <v>0.1745</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1492</v>
+        <v>-0.5456</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8989</v>
+        <v>-2.9932</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5239</v>
+        <v>-0.8328</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3751</v>
+        <v>-2.1604</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5127</v>
+        <v>-1.7964</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5543</v>
+        <v>0.0433</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0417</v>
+        <v>-1.8397</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3863</v>
+        <v>-1.1968</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0305</v>
+        <v>-0.8762</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4167</v>
+        <v>-0.3207</v>
       </c>
       <c r="P6" t="n">
-        <v>0.733</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
         <v>0.733</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6213</v>
+        <v>-0.0505</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5505</v>
+        <v>0.0313</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0708</v>
+        <v>-0.0818</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1267</v>
+        <v>2.8559</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.8559</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PENA</t>
+          <t>D. IGUAL BAU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9182</v>
+        <v>-0.8426</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6905</v>
+        <v>-0.967</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2276</v>
+        <v>0.1245</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.792</v>
+        <v>-0.8989</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2306</v>
+        <v>-0.5239</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0226</v>
+        <v>-0.3751</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1496</v>
+        <v>-0.5127</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9477</v>
+        <v>-0.5543</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.7981</v>
+        <v>0.0417</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9416</v>
+        <v>-0.3863</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.7171</v>
+        <v>0.0305</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2246</v>
+        <v>-0.4167</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5656</v>
+        <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0115</v>
+        <v>-0.55</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.4132</v>
+        <v>-0.4544</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4018</v>
+        <v>-0.0956</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3355</v>
+        <v>-0.1267</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2534</v>
+        <v>-0.1267</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9646</v>
+        <v>-1.039</v>
       </c>
       <c r="E8" t="n">
         <v>-0.963</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0016</v>
+        <v>-0.0759</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4023</v>
@@ -1078,13 +1078,13 @@
         <v>0.3665</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0126</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1101</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0975</v>
+        <v>0.0232</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5236</v>
+        <v>-1.6743</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0191</v>
+        <v>-2.2936</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4955</v>
+        <v>0.6193</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6131</v>
@@ -1156,13 +1156,13 @@
         <v>1.2828</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0449</v>
+        <v>-0.1058</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1637</v>
+        <v>-0.1108</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1188</v>
+        <v>0.0051</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3219</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1642</v>
+        <v>-2.8233</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7479</v>
+        <v>-1.5556</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4163</v>
+        <v>-1.2677</v>
       </c>
       <c r="G10" t="n">
         <v>-3.467</v>
@@ -1234,13 +1234,13 @@
         <v>0.733</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.781</v>
+        <v>-0.44</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3673</v>
+        <v>-0.175</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4137</v>
+        <v>-0.2651</v>
       </c>
       <c r="V10" t="n">
         <v>1.267</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5828</v>
+        <v>-4.0555</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8873</v>
+        <v>-3.1618</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6955</v>
+        <v>-0.8935999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3804</v>
@@ -1312,13 +1312,13 @@
         <v>2.9321</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3075</v>
+        <v>-0.1652</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1681</v>
+        <v>-0.4427</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4757</v>
+        <v>0.2775</v>
       </c>
       <c r="V11" t="n">
         <v>-1.51</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. DIAGNE</t>
+          <t>C. FUSTER ROYO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7969</v>
+        <v>-4.1715</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4545</v>
+        <v>-3.5003</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3424</v>
+        <v>-0.6712</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.0346</v>
+        <v>-3.0996</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.3389</v>
+        <v>-2.3173</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6957</v>
+        <v>-0.7823</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7267</v>
+        <v>-1.6447</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7684</v>
+        <v>-1.087</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0417</v>
+        <v>-0.5577</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.3079</v>
+        <v>-1.4549</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.5704</v>
+        <v>-1.2303</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.2246</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1833</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9163</v>
+        <v>-2.0158</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0995</v>
+        <v>1.8326</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3214</v>
+        <v>0.1831</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1886</v>
+        <v>-0.1617</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1329</v>
+        <v>0.3448</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.267</v>
+        <v>-1.0717</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.267</v>
+        <v>-1.3937</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. FUSTER ROYO</t>
+          <t>E. DIAGNE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8367</v>
+        <v>-4.8351</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0912</v>
+        <v>-1.4432</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-3.392</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.0996</v>
+        <v>-4.0346</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.3173</v>
+        <v>-3.3389</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7823</v>
+        <v>-0.6957</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.6447</v>
+        <v>-0.7267</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.087</v>
+        <v>-0.7684</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5577</v>
+        <v>0.0417</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4549</v>
+        <v>-3.3079</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2303</v>
+        <v>-2.5704</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2246</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1833</v>
+        <v>0.1833</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0158</v>
+        <v>-0.9163</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8326</v>
+        <v>1.0995</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4821</v>
+        <v>0.2832</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7526</v>
+        <v>0.1999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2705</v>
+        <v>0.0833</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0717</v>
+        <v>-1.267</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.3937</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="14">
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-16.5501</v>
+        <v>-15.7245</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.152100000000001</v>
+        <v>-7.326200000000001</v>
       </c>
       <c r="F14" t="n">
         <v>-8.398099999999999</v>
@@ -1516,13 +1516,13 @@
         <v>-11.4783</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.7693</v>
+        <v>-5.769300000000001</v>
       </c>
       <c r="J14" t="n">
         <v>1.7201</v>
       </c>
       <c r="K14" t="n">
-        <v>5.404400000000002</v>
+        <v>5.404400000000001</v>
       </c>
       <c r="L14" t="n">
         <v>-3.684</v>
@@ -1546,22 +1546,22 @@
         <v>17.4094</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.0279</v>
+        <v>-2.2021</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.4988</v>
+        <v>-2.6734</v>
       </c>
       <c r="U14" t="n">
         <v>0.4712</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9761999999999997</v>
+        <v>0.9762</v>
       </c>
       <c r="W14" t="n">
         <v>8.2874</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.311100000000001</v>
+        <v>-7.3111</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.6319</v>
+        <v>7.1142</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4766</v>
+        <v>5.3805</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1553</v>
+        <v>1.7337</v>
       </c>
       <c r="G15" t="n">
         <v>6.731</v>
@@ -1624,13 +1624,13 @@
         <v>1.8326</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0133</v>
+        <v>0.4957</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1086</v>
+        <v>0.0125</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0953</v>
+        <v>0.4832</v>
       </c>
       <c r="V15" t="n">
         <v>-1.5785</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. VIDAL BALDOVI</t>
+          <t>B. BREM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.6762</v>
+        <v>4.317</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2464</v>
+        <v>5.2529</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4298</v>
+        <v>-0.9359</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4803</v>
+        <v>3.0617</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3038</v>
+        <v>0.8144</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1764</v>
+        <v>2.2472</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3662</v>
+        <v>4.0417</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2473</v>
+        <v>1.4739</v>
       </c>
       <c r="L16" t="n">
-        <v>0.119</v>
+        <v>2.5679</v>
       </c>
       <c r="M16" t="n">
-        <v>0.114</v>
+        <v>-0.9801</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9434</v>
+        <v>-0.6594</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0575</v>
+        <v>-0.3207</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1833</v>
+        <v>1.0995</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.2828</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0676</v>
+        <v>-0.1557</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5294</v>
+        <v>-0.0558</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5382</v>
+        <v>-0.0999</v>
       </c>
       <c r="V16" t="n">
-        <v>0.945</v>
+        <v>0.3115</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6335</v>
+        <v>1.267</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3115</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. BREM</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8828</v>
+        <v>4.1247</v>
       </c>
       <c r="E17" t="n">
-        <v>4.8683</v>
+        <v>0.0038</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9855</v>
+        <v>4.121</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0617</v>
+        <v>1.9454</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8144</v>
+        <v>0.9232</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2472</v>
+        <v>1.0222</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0417</v>
+        <v>1.9917</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4739</v>
+        <v>1.8666</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5679</v>
+        <v>0.125</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9801</v>
+        <v>-0.0463</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6594</v>
+        <v>-0.9434</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3207</v>
+        <v>0.8971</v>
       </c>
       <c r="P17" t="n">
-        <v>1.0995</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.1154</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0995</v>
+        <v>2.7489</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5899</v>
+        <v>0.9674</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4404</v>
+        <v>-0.1395</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1495</v>
+        <v>1.1069</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3115</v>
+        <v>1.5785</v>
       </c>
       <c r="W17" t="n">
         <v>1.267</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9554</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>S. VIDAL BALDOVI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.5521</v>
+        <v>4.0714</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1885</v>
+        <v>1.0541</v>
       </c>
       <c r="F18" t="n">
-        <v>3.7407</v>
+        <v>3.0173</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9454</v>
+        <v>1.4803</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9232</v>
+        <v>0.3038</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0222</v>
+        <v>1.1764</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9917</v>
+        <v>1.3662</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8666</v>
+        <v>1.2473</v>
       </c>
       <c r="L18" t="n">
-        <v>0.125</v>
+        <v>0.119</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0463</v>
+        <v>0.114</v>
       </c>
       <c r="N18" t="n">
         <v>-0.9434</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8971</v>
+        <v>1.0575</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1154</v>
+        <v>-1.2828</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7489</v>
+        <v>1.4661</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3948</v>
+        <v>1.4628</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3318</v>
+        <v>0.3371</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7266</v>
+        <v>1.1257</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5785</v>
+        <v>0.945</v>
       </c>
       <c r="W18" t="n">
-        <v>1.267</v>
+        <v>0.6335</v>
       </c>
       <c r="X18" t="n">
         <v>0.3115</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0041</v>
+        <v>2.3087</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9647</v>
+        <v>0.8685</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0395</v>
+        <v>1.4402</v>
       </c>
       <c r="G19" t="n">
         <v>0.1867</v>
@@ -1936,13 +1936,13 @@
         <v>1.4661</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7495000000000001</v>
+        <v>1.0541</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2738</v>
+        <v>0.1776</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4758</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>2.5339</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.7237</v>
+        <v>1.8504</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7211</v>
+        <v>-1.5288</v>
       </c>
       <c r="F20" t="n">
-        <v>3.4448</v>
+        <v>3.3792</v>
       </c>
       <c r="G20" t="n">
         <v>2.3844</v>
@@ -2014,13 +2014,13 @@
         <v>2.7489</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9233</v>
+        <v>1.0499</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3318</v>
+        <v>-0.1395</v>
       </c>
       <c r="U20" t="n">
-        <v>1.2551</v>
+        <v>1.1894</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3011</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.293</v>
+        <v>0.9331</v>
       </c>
       <c r="E22" t="n">
-        <v>1.487</v>
+        <v>1.1024</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.194</v>
+        <v>-0.1693</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0162</v>
@@ -2170,13 +2170,13 @@
         <v>0.1833</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4924</v>
+        <v>0.1325</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4759</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="V22" t="n">
         <v>0.6335</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4097</v>
+        <v>-0.3354</v>
       </c>
       <c r="E23" t="n">
         <v>-0.08840000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3213</v>
+        <v>-0.247</v>
       </c>
       <c r="G23" t="n">
         <v>-0.0272</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0606</v>
+        <v>0.0138</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1101</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0495</v>
+        <v>0.1239</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3219</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6692</v>
+        <v>-0.8833</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3254</v>
+        <v>-0.6139</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3438</v>
+        <v>-0.2694</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9458</v>
@@ -2326,13 +2326,13 @@
         <v>0.733</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1345</v>
+        <v>-0.3486</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1456</v>
+        <v>-0.1429</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.28</v>
+        <v>-0.2057</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3219</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7704</v>
+        <v>-1.0312</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3601</v>
+        <v>-1.7447</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5897</v>
+        <v>0.7135</v>
       </c>
       <c r="G25" t="n">
         <v>-0.1743</v>
@@ -2404,13 +2404,13 @@
         <v>0.9163</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3201</v>
+        <v>0.0594</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3658</v>
+        <v>-0.0188</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0456</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.0437</v>
+        <v>-2.4041</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.9793</v>
+        <v>-2.6908</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0644</v>
+        <v>0.2867</v>
       </c>
       <c r="G26" t="n">
         <v>0.604</v>
@@ -2482,13 +2482,13 @@
         <v>1.0995</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8596</v>
+        <v>-0.22</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6056</v>
+        <v>-0.3171</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2541</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9554</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.9212</v>
+        <v>-3.8338</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.5825</v>
+        <v>-0.1978</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.3387</v>
+        <v>-3.636</v>
       </c>
       <c r="G27" t="n">
         <v>0.4171</v>
@@ -2560,13 +2560,13 @@
         <v>0.3665</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.2887</v>
+        <v>-0.2014</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.5505</v>
+        <v>-0.1659</v>
       </c>
       <c r="U27" t="n">
-        <v>0.2618</v>
+        <v>-0.0355</v>
       </c>
       <c r="V27" t="n">
         <v>-3.4998</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>16.5501</v>
+        <v>17.8322</v>
       </c>
       <c r="E28" t="n">
-        <v>8.398199999999997</v>
+        <v>8.398300000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>8.152100000000003</v>
+        <v>9.434000000000001</v>
       </c>
       <c r="G28" t="n">
         <v>17.2476</v>
@@ -2629,7 +2629,7 @@
         <v>3.683900000000001</v>
       </c>
       <c r="P28" t="n">
-        <v>-2.7489</v>
+        <v>-2.748899999999999</v>
       </c>
       <c r="Q28" t="n">
         <v>-17.4095</v>
@@ -2638,13 +2638,13 @@
         <v>14.6607</v>
       </c>
       <c r="S28" t="n">
-        <v>3.0277</v>
+        <v>4.309900000000001</v>
       </c>
       <c r="T28" t="n">
         <v>-0.4711</v>
       </c>
       <c r="U28" t="n">
-        <v>3.499000000000001</v>
+        <v>4.7811</v>
       </c>
       <c r="V28" t="n">
         <v>-0.9762</v>
